--- a/Retail Sales Analysis and Dashboard using Excel.xlsx
+++ b/Retail Sales Analysis and Dashboard using Excel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC World\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{250FA5F6-6591-43D5-9925-2045444E9D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCBCC8F4-6731-4CAC-878E-30A5394B28E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -1225,7 +1225,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -1406,7 +1406,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1421,7 +1421,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1445,7 +1445,7 @@
     <xf numFmtId="14" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1454,7 +1454,7 @@
     <xf numFmtId="44" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1464,21 +1464,20 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" pivotButton="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" pivotButton="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1487,4231 +1486,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="829">
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
+  <dxfs count="61">
     <dxf>
       <border>
         <left style="thin">
@@ -6217,3667 +1992,7 @@
       </font>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
     </dxf>
     <dxf>
       <border>
@@ -11262,19 +3377,7 @@
           <a:sp3d/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent4"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -13282,8 +5385,8 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>14884</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="6" name="Year 1">
@@ -13306,7 +5409,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -13360,8 +5463,8 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>74414</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="7" name="Region 1">
@@ -13384,7 +5487,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -13438,8 +5541,8 @@
       <xdr:row>37</xdr:row>
       <xdr:rowOff>127991</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="8" name="Category 1">
@@ -13462,7 +5565,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -13590,7 +5693,7 @@
     <cacheField name="Product Name" numFmtId="0">
       <sharedItems containsNonDate="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="Sales" numFmtId="166">
+    <cacheField name="Sales" numFmtId="164">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="3083.43" count="49">
         <n v="261.95999999999998"/>
         <n v="14.62"/>
@@ -14952,835 +7055,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000004000000}" name="PivotTable17" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15" rowHeaderCaption="Discount">
-  <location ref="A34:B37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="23">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0" sortType="descending">
-      <items count="6">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="4"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="50">
-        <item x="34"/>
-        <item x="31"/>
-        <item x="45"/>
-        <item x="9"/>
-        <item x="13"/>
-        <item x="44"/>
-        <item x="27"/>
-        <item x="1"/>
-        <item x="37"/>
-        <item x="25"/>
-        <item x="4"/>
-        <item x="32"/>
-        <item x="35"/>
-        <item x="10"/>
-        <item x="41"/>
-        <item x="43"/>
-        <item x="15"/>
-        <item x="24"/>
-        <item x="23"/>
-        <item x="21"/>
-        <item x="3"/>
-        <item x="47"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="11"/>
-        <item x="30"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="46"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="42"/>
-        <item x="38"/>
-        <item x="36"/>
-        <item x="26"/>
-        <item x="22"/>
-        <item x="28"/>
-        <item x="39"/>
-        <item x="0"/>
-        <item x="40"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item x="33"/>
-        <item x="2"/>
-        <item x="12"/>
-        <item x="16"/>
-        <item x="29"/>
-        <item x="14"/>
-        <item x="48"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Sales" fld="19" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="12">
-    <format dxfId="779">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="778">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="777">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="776">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="775">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="774">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="773">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="772">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="771">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="770">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="769">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="768">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="6" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000003000000}" name="PivotTable15" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11" rowHeaderCaption="Discount">
-  <location ref="A23:B25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="23">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="6">
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item h="1" x="4"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="50">
-        <item x="34"/>
-        <item x="31"/>
-        <item x="45"/>
-        <item x="9"/>
-        <item x="13"/>
-        <item x="44"/>
-        <item x="27"/>
-        <item x="1"/>
-        <item x="37"/>
-        <item x="25"/>
-        <item x="4"/>
-        <item x="32"/>
-        <item x="35"/>
-        <item x="10"/>
-        <item x="41"/>
-        <item x="43"/>
-        <item x="15"/>
-        <item x="24"/>
-        <item x="23"/>
-        <item x="21"/>
-        <item x="3"/>
-        <item x="47"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="11"/>
-        <item x="30"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="46"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="42"/>
-        <item x="38"/>
-        <item x="36"/>
-        <item x="26"/>
-        <item x="22"/>
-        <item x="28"/>
-        <item x="39"/>
-        <item x="0"/>
-        <item x="40"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item x="33"/>
-        <item x="2"/>
-        <item x="12"/>
-        <item x="16"/>
-        <item x="29"/>
-        <item x="14"/>
-        <item x="48"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="14"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Sales" fld="19" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="12">
-    <format dxfId="791">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="790">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="789">
-      <pivotArea field="14" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="788">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="14" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="787">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="786">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="785">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="784">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="783">
-      <pivotArea field="14" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="782">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="14" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="781">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="780">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000002000000}" name="PivotTable14" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="24" rowHeaderCaption="Discount">
-  <location ref="A13:B15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="23">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item h="1" x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="5">
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="50">
-        <item x="14"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="33"/>
-        <item x="39"/>
-        <item x="28"/>
-        <item x="35"/>
-        <item x="45"/>
-        <item x="34"/>
-        <item x="11"/>
-        <item x="31"/>
-        <item x="9"/>
-        <item x="19"/>
-        <item x="37"/>
-        <item x="13"/>
-        <item x="23"/>
-        <item x="10"/>
-        <item x="4"/>
-        <item x="27"/>
-        <item x="44"/>
-        <item x="25"/>
-        <item x="43"/>
-        <item x="41"/>
-        <item x="1"/>
-        <item x="22"/>
-        <item x="32"/>
-        <item x="20"/>
-        <item x="15"/>
-        <item x="8"/>
-        <item x="7"/>
-        <item x="42"/>
-        <item x="3"/>
-        <item x="18"/>
-        <item x="47"/>
-        <item x="24"/>
-        <item x="21"/>
-        <item x="40"/>
-        <item x="17"/>
-        <item x="30"/>
-        <item x="46"/>
-        <item x="0"/>
-        <item x="26"/>
-        <item x="36"/>
-        <item x="38"/>
-        <item x="29"/>
-        <item x="16"/>
-        <item x="5"/>
-        <item x="12"/>
-        <item x="48"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="16"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Profit" fld="22" baseField="16" baseItem="0"/>
-  </dataFields>
-  <formats count="13">
-    <format dxfId="804">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="803">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="802">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="801">
-      <pivotArea field="16" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="800">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="16" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="799">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="798">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="797">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="796">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="795">
-      <pivotArea field="16" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="794">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="16" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="793">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="792">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="PivotTable13" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17" rowHeaderCaption="Discount">
-  <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="23">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item h="1" x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="5">
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="50">
-        <item x="34"/>
-        <item x="31"/>
-        <item x="45"/>
-        <item x="9"/>
-        <item x="13"/>
-        <item x="44"/>
-        <item x="27"/>
-        <item x="1"/>
-        <item x="37"/>
-        <item x="25"/>
-        <item x="4"/>
-        <item x="32"/>
-        <item x="35"/>
-        <item x="10"/>
-        <item x="41"/>
-        <item x="43"/>
-        <item x="15"/>
-        <item x="24"/>
-        <item x="23"/>
-        <item x="21"/>
-        <item x="3"/>
-        <item x="47"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="11"/>
-        <item x="30"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="46"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="42"/>
-        <item x="38"/>
-        <item x="36"/>
-        <item x="26"/>
-        <item x="22"/>
-        <item x="28"/>
-        <item x="39"/>
-        <item x="0"/>
-        <item x="40"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item x="33"/>
-        <item x="2"/>
-        <item x="12"/>
-        <item x="16"/>
-        <item x="29"/>
-        <item x="14"/>
-        <item x="48"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="16"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Sales" fld="19" baseField="16" baseItem="0"/>
-  </dataFields>
-  <formats count="12">
-    <format dxfId="816">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="815">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="814">
-      <pivotArea field="16" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="813">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="16" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="812">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="811">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="810">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="809">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="808">
-      <pivotArea field="16" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="807">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="16" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="806">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="805">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="1">
-    <chartFormat chart="10" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable21" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Discount">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable21" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Discount">
   <location ref="A43:B52" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="23">
     <pivotField showAll="0"/>
@@ -15973,51 +7248,879 @@
     <dataField name="Sum of Profit" fld="22" baseField="21" baseItem="0"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="828">
+    <format dxfId="11">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="827">
+    <format dxfId="10">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="826">
+    <format dxfId="9">
       <pivotArea field="21" type="button" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="825">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="21" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="824">
+    <format dxfId="7">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="823">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="822">
+    <format dxfId="5">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="821">
+    <format dxfId="4">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="820">
+    <format dxfId="3">
       <pivotArea field="21" type="button" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="819">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="21" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="818">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="817">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000004000000}" name="PivotTable17" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15" rowHeaderCaption="Discount">
+  <location ref="A34:B37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="23">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0" sortType="descending">
+      <items count="6">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="50">
+        <item x="34"/>
+        <item x="31"/>
+        <item x="45"/>
+        <item x="9"/>
+        <item x="13"/>
+        <item x="44"/>
+        <item x="27"/>
+        <item x="1"/>
+        <item x="37"/>
+        <item x="25"/>
+        <item x="4"/>
+        <item x="32"/>
+        <item x="35"/>
+        <item x="10"/>
+        <item x="41"/>
+        <item x="43"/>
+        <item x="15"/>
+        <item x="24"/>
+        <item x="23"/>
+        <item x="21"/>
+        <item x="3"/>
+        <item x="47"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="11"/>
+        <item x="30"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="46"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="42"/>
+        <item x="38"/>
+        <item x="36"/>
+        <item x="26"/>
+        <item x="22"/>
+        <item x="28"/>
+        <item x="39"/>
+        <item x="0"/>
+        <item x="40"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item x="33"/>
+        <item x="2"/>
+        <item x="12"/>
+        <item x="16"/>
+        <item x="29"/>
+        <item x="14"/>
+        <item x="48"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Sales" fld="19" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="12">
+    <format dxfId="23">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="22">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="17">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="15">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="6" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000003000000}" name="PivotTable15" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11" rowHeaderCaption="Discount">
+  <location ref="A23:B25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="23">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="6">
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="50">
+        <item x="34"/>
+        <item x="31"/>
+        <item x="45"/>
+        <item x="9"/>
+        <item x="13"/>
+        <item x="44"/>
+        <item x="27"/>
+        <item x="1"/>
+        <item x="37"/>
+        <item x="25"/>
+        <item x="4"/>
+        <item x="32"/>
+        <item x="35"/>
+        <item x="10"/>
+        <item x="41"/>
+        <item x="43"/>
+        <item x="15"/>
+        <item x="24"/>
+        <item x="23"/>
+        <item x="21"/>
+        <item x="3"/>
+        <item x="47"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="11"/>
+        <item x="30"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="46"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="42"/>
+        <item x="38"/>
+        <item x="36"/>
+        <item x="26"/>
+        <item x="22"/>
+        <item x="28"/>
+        <item x="39"/>
+        <item x="0"/>
+        <item x="40"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item x="33"/>
+        <item x="2"/>
+        <item x="12"/>
+        <item x="16"/>
+        <item x="29"/>
+        <item x="14"/>
+        <item x="48"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="14"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Sales" fld="19" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="12">
+    <format dxfId="35">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="34">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="33">
+      <pivotArea field="14" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="32">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="14" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="31">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="30">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="29">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="28">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="27">
+      <pivotArea field="14" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="26">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="14" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="25">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="24">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000002000000}" name="PivotTable14" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="24" rowHeaderCaption="Discount">
+  <location ref="A13:B15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="23">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="5">
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="50">
+        <item x="14"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="33"/>
+        <item x="39"/>
+        <item x="28"/>
+        <item x="35"/>
+        <item x="45"/>
+        <item x="34"/>
+        <item x="11"/>
+        <item x="31"/>
+        <item x="9"/>
+        <item x="19"/>
+        <item x="37"/>
+        <item x="13"/>
+        <item x="23"/>
+        <item x="10"/>
+        <item x="4"/>
+        <item x="27"/>
+        <item x="44"/>
+        <item x="25"/>
+        <item x="43"/>
+        <item x="41"/>
+        <item x="1"/>
+        <item x="22"/>
+        <item x="32"/>
+        <item x="20"/>
+        <item x="15"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item x="42"/>
+        <item x="3"/>
+        <item x="18"/>
+        <item x="47"/>
+        <item x="24"/>
+        <item x="21"/>
+        <item x="40"/>
+        <item x="17"/>
+        <item x="30"/>
+        <item x="46"/>
+        <item x="0"/>
+        <item x="26"/>
+        <item x="36"/>
+        <item x="38"/>
+        <item x="29"/>
+        <item x="16"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="48"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="16"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Profit" fld="22" baseField="16" baseItem="0"/>
+  </dataFields>
+  <formats count="13">
+    <format dxfId="48">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="47">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="46">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="45">
+      <pivotArea field="16" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="44">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="16" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="43">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="42">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="41">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="40">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="39">
+      <pivotArea field="16" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="38">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="16" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="37">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="36">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="PivotTable13" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17" rowHeaderCaption="Discount">
+  <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="23">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="5">
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="50">
+        <item x="34"/>
+        <item x="31"/>
+        <item x="45"/>
+        <item x="9"/>
+        <item x="13"/>
+        <item x="44"/>
+        <item x="27"/>
+        <item x="1"/>
+        <item x="37"/>
+        <item x="25"/>
+        <item x="4"/>
+        <item x="32"/>
+        <item x="35"/>
+        <item x="10"/>
+        <item x="41"/>
+        <item x="43"/>
+        <item x="15"/>
+        <item x="24"/>
+        <item x="23"/>
+        <item x="21"/>
+        <item x="3"/>
+        <item x="47"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="11"/>
+        <item x="30"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="46"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="42"/>
+        <item x="38"/>
+        <item x="36"/>
+        <item x="26"/>
+        <item x="22"/>
+        <item x="28"/>
+        <item x="39"/>
+        <item x="0"/>
+        <item x="40"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item x="33"/>
+        <item x="2"/>
+        <item x="12"/>
+        <item x="16"/>
+        <item x="29"/>
+        <item x="14"/>
+        <item x="48"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="16"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Sales" fld="19" baseField="16" baseItem="0"/>
+  </dataFields>
+  <formats count="12">
+    <format dxfId="60">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="59">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="58">
+      <pivotArea field="16" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="57">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="16" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="56">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="55">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="54">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="53">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="52">
+      <pivotArea field="16" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="51">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="16" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="50">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="49">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="10" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -23172,31 +15275,29 @@
       <c r="B2" s="3"/>
     </row>
     <row r="3" spans="1:2" ht="15.75">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="34" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="36">
+      <c r="B4" s="35">
         <v>395.20799999999997</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="38" t="s">
         <v>374</v>
       </c>
-      <c r="B5" s="37">
+      <c r="B5" s="36">
         <v>395.20799999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75"/>
-    <row r="7" spans="1:2" ht="15.75"/>
     <row r="8" spans="1:2">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
@@ -23220,31 +15321,29 @@
       <c r="B12" s="3"/>
     </row>
     <row r="13" spans="1:2" ht="15.75">
-      <c r="A13" s="38" t="s">
+      <c r="A13" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="34" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.75">
-      <c r="A14" s="39" t="s">
+      <c r="A14" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="36">
+      <c r="B14" s="35">
         <v>106.87160000000002</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.75">
-      <c r="A15" s="39" t="s">
+      <c r="A15" s="38" t="s">
         <v>374</v>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="36">
         <v>106.87160000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75"/>
-    <row r="17" spans="1:2" ht="15.75"/>
     <row r="18" spans="1:2">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
@@ -23268,32 +15367,29 @@
       <c r="B22" s="3"/>
     </row>
     <row r="23" spans="1:2" ht="15.75">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="35" t="s">
+      <c r="B23" s="34" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15.75">
-      <c r="A24" s="39" t="s">
+      <c r="A24" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="36">
+      <c r="B24" s="35">
         <v>395.20799999999997</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15.75">
-      <c r="A25" s="39" t="s">
+      <c r="A25" s="38" t="s">
         <v>374</v>
       </c>
-      <c r="B25" s="37">
+      <c r="B25" s="36">
         <v>395.20799999999997</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75"/>
-    <row r="27" spans="1:2" ht="15.75"/>
-    <row r="28" spans="1:2" ht="15.75"/>
     <row r="29" spans="1:2">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
@@ -23457,15 +15553,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E60AB4D-1635-486F-8E9B-E0DBE54FF7F8}">
-  <dimension ref="B1:C2"/>
+  <dimension ref="C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:3">
-      <c r="B1" s="33"/>
-    </row>
-    <row r="2" spans="2:3">
-      <c r="B2" s="33"/>
-      <c r="C2" s="34"/>
+    <row r="2" spans="3:3">
+      <c r="C2" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
